--- a/questions.xlsx
+++ b/questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NANCY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NANCY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D30C885-9430-4189-A054-30D67795605C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BD390F6-6F07-41C8-A0B2-AFEB4F1EE9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="192" windowWidth="21384" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="題庫" sheetId="1" r:id="rId1"/>
@@ -14889,9 +14889,6 @@
     <t>Q0797</t>
   </si>
   <si>
-    <t>若企業在廠區內種植樹木（碳匯），並計算其碳移除量（Removal）。在填寫排放清冊時，這筆移除量應如何處理？ 115 年第一次淨零碳規劃管理師-初級能力鑑定【公告試題】 第二科：淨零碳盤查規範與程序概要考試日期：115 年 05 月 16 日第 6 頁，共 10 頁答案題目</t>
-  </si>
-  <si>
     <t>直接與排放量相減，申報淨排放量</t>
   </si>
   <si>
@@ -15205,9 +15202,6 @@
   </si>
   <si>
     <t>Q0813</t>
-  </si>
-  <si>
-    <t>根據環境部碳足跡產品類別規則訂定、引用及修訂指引規定，要求在取得環境部文件登錄編號後，產品類別規則（PCR）應在下列何時內制定完成，以提送工作 115 年第一次淨零碳規劃管理師-初級能力鑑定【公告試題】 第二科：淨零碳盤查規範與程序概要考試日期：115 年 05 月 16 日第 9 頁，共 10 頁答案題目小組審查？</t>
   </si>
   <si>
     <t>60 個工作天內</t>
@@ -18253,6 +18247,72 @@
       </rPr>
       <t xml:space="preserve">
 </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>若企業在廠區內種植樹木（碳匯），並計算其碳移除量（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Removal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）。在填寫排放清冊時，這筆移除量應如何處理？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>根據環境部碳足跡產品類別規則訂定、引用及修訂指引規定，要求在取得環境部文件登錄編號後，產品類別規則（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PCR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）應在下列何時內制定完成，以提送工作小組審查？</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -29883,7 +29943,7 @@
         <v>1754</v>
       </c>
       <c r="I268" s="7" t="s">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>1755</v>
@@ -29892,10 +29952,10 @@
         <v>1756</v>
       </c>
       <c r="L268" s="4" t="s">
+        <v>5141</v>
+      </c>
+      <c r="M268" s="6" t="s">
         <v>5143</v>
-      </c>
-      <c r="M268" s="6" t="s">
-        <v>5145</v>
       </c>
       <c r="N268" s="2" t="s">
         <v>25</v>
@@ -30138,16 +30198,16 @@
         <v>364</v>
       </c>
       <c r="J274" s="7" t="s">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="K274" s="2" t="s">
         <v>366</v>
       </c>
       <c r="L274" s="4" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="M274" s="6" t="s">
-        <v>5147</v>
+        <v>5145</v>
       </c>
       <c r="N274" s="2" t="s">
         <v>25</v>
@@ -30270,10 +30330,10 @@
         <v>1370</v>
       </c>
       <c r="L277" s="4" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="M277" s="6" t="s">
-        <v>5149</v>
+        <v>5147</v>
       </c>
       <c r="N277" s="2" t="s">
         <v>25</v>
@@ -31014,7 +31074,7 @@
         <v>1919</v>
       </c>
       <c r="H295" s="7" t="s">
-        <v>5151</v>
+        <v>5149</v>
       </c>
       <c r="I295" s="2" t="s">
         <v>290</v>
@@ -31026,10 +31086,10 @@
         <v>1921</v>
       </c>
       <c r="L295" s="4" t="s">
+        <v>5148</v>
+      </c>
+      <c r="M295" s="6" t="s">
         <v>5150</v>
-      </c>
-      <c r="M295" s="6" t="s">
-        <v>5152</v>
       </c>
       <c r="N295" s="2" t="s">
         <v>25</v>
@@ -31056,10 +31116,10 @@
         <v>1923</v>
       </c>
       <c r="H296" s="6" t="s">
-        <v>5153</v>
+        <v>5151</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>5158</v>
+        <v>5156</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>1924</v>
@@ -31068,10 +31128,10 @@
         <v>1925</v>
       </c>
       <c r="L296" s="4" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="M296" s="6" t="s">
-        <v>5159</v>
+        <v>5157</v>
       </c>
       <c r="N296" s="2" t="s">
         <v>25</v>
@@ -31146,16 +31206,16 @@
         <v>1936</v>
       </c>
       <c r="J298" s="7" t="s">
-        <v>5154</v>
+        <v>5152</v>
       </c>
       <c r="K298" s="2" t="s">
         <v>1937</v>
       </c>
       <c r="L298" s="4" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="M298" s="6" t="s">
-        <v>5155</v>
+        <v>5153</v>
       </c>
       <c r="N298" s="2" t="s">
         <v>25</v>
@@ -31191,13 +31251,13 @@
         <v>1942</v>
       </c>
       <c r="K299" s="7" t="s">
-        <v>5156</v>
+        <v>5154</v>
       </c>
       <c r="L299" s="4" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="M299" s="6" t="s">
-        <v>5157</v>
+        <v>5155</v>
       </c>
       <c r="N299" s="2" t="s">
         <v>25</v>
@@ -31272,16 +31332,16 @@
         <v>1953</v>
       </c>
       <c r="J301" s="7" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="K301" s="2" t="s">
         <v>1954</v>
       </c>
       <c r="L301" s="4" t="s">
+        <v>5138</v>
+      </c>
+      <c r="M301" s="6" t="s">
         <v>5140</v>
-      </c>
-      <c r="M301" s="6" t="s">
-        <v>5142</v>
       </c>
       <c r="N301" s="2" t="s">
         <v>25</v>
@@ -31353,7 +31413,7 @@
         <v>1964</v>
       </c>
       <c r="I303" s="2" t="s">
-        <v>5160</v>
+        <v>5158</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>1965</v>
@@ -31362,10 +31422,10 @@
         <v>1966</v>
       </c>
       <c r="L303" s="4" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="M303" s="6" t="s">
-        <v>5161</v>
+        <v>5159</v>
       </c>
       <c r="N303" s="2" t="s">
         <v>25</v>
@@ -31404,10 +31464,10 @@
         <v>321</v>
       </c>
       <c r="L304" s="4" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="M304" s="6" t="s">
-        <v>5162</v>
+        <v>5160</v>
       </c>
       <c r="N304" s="2" t="s">
         <v>25</v>
@@ -32193,7 +32253,7 @@
         <v>2045</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>5163</v>
+        <v>5161</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>2046</v>
@@ -32202,10 +32262,10 @@
         <v>2047</v>
       </c>
       <c r="L323" s="4" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="M323" s="6" t="s">
-        <v>5164</v>
+        <v>5162</v>
       </c>
       <c r="N323" s="2" t="s">
         <v>25</v>
@@ -32274,7 +32334,7 @@
         <v>2056</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>5165</v>
+        <v>5163</v>
       </c>
       <c r="I325" s="2" t="s">
         <v>2057</v>
@@ -32319,19 +32379,19 @@
         <v>2061</v>
       </c>
       <c r="I326" s="7" t="s">
-        <v>5168</v>
+        <v>5166</v>
       </c>
       <c r="J326" s="2" t="s">
-        <v>5166</v>
+        <v>5164</v>
       </c>
       <c r="K326" s="7" t="s">
+        <v>5165</v>
+      </c>
+      <c r="L326" s="4" t="s">
+        <v>5141</v>
+      </c>
+      <c r="M326" s="6" t="s">
         <v>5167</v>
-      </c>
-      <c r="L326" s="4" t="s">
-        <v>5143</v>
-      </c>
-      <c r="M326" s="6" t="s">
-        <v>5169</v>
       </c>
       <c r="N326" s="2" t="s">
         <v>25</v>
@@ -32361,10 +32421,10 @@
         <v>2065</v>
       </c>
       <c r="I327" s="7" t="s">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="J327" s="7" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
       <c r="K327" s="2" t="s">
         <v>2066</v>
@@ -32373,7 +32433,7 @@
         <v>47</v>
       </c>
       <c r="M327" s="6" t="s">
-        <v>5172</v>
+        <v>5170</v>
       </c>
       <c r="N327" s="2" t="s">
         <v>25</v>
@@ -32451,7 +32511,7 @@
         <v>2075</v>
       </c>
       <c r="K329" s="7" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="L329" s="4" t="s">
         <v>47</v>
@@ -32496,10 +32556,10 @@
         <v>2082</v>
       </c>
       <c r="L330" s="4" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="M330" s="6" t="s">
-        <v>5173</v>
+        <v>5171</v>
       </c>
       <c r="N330" s="2" t="s">
         <v>25</v>
@@ -32619,13 +32679,13 @@
         <v>4153</v>
       </c>
       <c r="K333" s="8" t="s">
-        <v>5174</v>
+        <v>5172</v>
       </c>
       <c r="L333" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M333" s="6" t="s">
-        <v>5175</v>
+        <v>5173</v>
       </c>
       <c r="N333" s="2" t="s">
         <v>25</v>
@@ -32661,7 +32721,7 @@
         <v>2105</v>
       </c>
       <c r="K334" s="6" t="s">
-        <v>5130</v>
+        <v>5128</v>
       </c>
       <c r="L334" s="4" t="s">
         <v>47</v>
@@ -32865,16 +32925,16 @@
         <v>2136</v>
       </c>
       <c r="I339" s="7" t="s">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="J339" s="7" t="s">
-        <v>5177</v>
+        <v>5175</v>
       </c>
       <c r="K339" s="6" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="L339" s="4" t="s">
-        <v>5150</v>
+        <v>5148</v>
       </c>
       <c r="M339" s="2" t="s">
         <v>2137</v>
@@ -33039,7 +33099,7 @@
         <v>2163</v>
       </c>
       <c r="K343" s="6" t="s">
-        <v>5133</v>
+        <v>5131</v>
       </c>
       <c r="L343" s="4" t="s">
         <v>32</v>
@@ -33207,13 +33267,13 @@
         <v>2186</v>
       </c>
       <c r="K347" s="7" t="s">
-        <v>5132</v>
+        <v>5130</v>
       </c>
       <c r="L347" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M347" s="6" t="s">
-        <v>5134</v>
+        <v>5132</v>
       </c>
       <c r="N347" s="2" t="s">
         <v>25</v>
@@ -33237,28 +33297,28 @@
         <v>347</v>
       </c>
       <c r="G348" s="10" t="s">
+        <v>5176</v>
+      </c>
+      <c r="H348" s="10" t="s">
+        <v>5177</v>
+      </c>
+      <c r="I348" s="10" t="s">
         <v>5178</v>
       </c>
-      <c r="H348" s="10" t="s">
+      <c r="J348" s="13" t="s">
+        <v>5182</v>
+      </c>
+      <c r="K348" s="10" t="s">
         <v>5179</v>
-      </c>
-      <c r="I348" s="10" t="s">
-        <v>5180</v>
-      </c>
-      <c r="J348" s="13" t="s">
-        <v>5184</v>
-      </c>
-      <c r="K348" s="10" t="s">
-        <v>5181</v>
       </c>
       <c r="L348" s="11" t="s">
         <v>47</v>
       </c>
       <c r="M348" s="10" t="s">
-        <v>5182</v>
+        <v>5180</v>
       </c>
       <c r="N348" s="10" t="s">
-        <v>5183</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="349" spans="1:14" ht="42">
@@ -33282,7 +33342,7 @@
         <v>2189</v>
       </c>
       <c r="H349" s="6" t="s">
-        <v>5185</v>
+        <v>5183</v>
       </c>
       <c r="I349" s="2" t="s">
         <v>2190</v>
@@ -33297,7 +33357,7 @@
         <v>23</v>
       </c>
       <c r="M349" s="6" t="s">
-        <v>5186</v>
+        <v>5184</v>
       </c>
       <c r="N349" s="2" t="s">
         <v>25</v>
@@ -33417,7 +33477,7 @@
         <v>2207</v>
       </c>
       <c r="K352" s="6" t="s">
-        <v>5135</v>
+        <v>5133</v>
       </c>
       <c r="L352" s="4" t="s">
         <v>23</v>
@@ -33453,10 +33513,10 @@
         <v>2211</v>
       </c>
       <c r="I353" s="8" t="s">
-        <v>5189</v>
+        <v>5187</v>
       </c>
       <c r="J353" s="8" t="s">
-        <v>5187</v>
+        <v>5185</v>
       </c>
       <c r="K353" s="2" t="s">
         <v>1453</v>
@@ -33465,7 +33525,7 @@
         <v>47</v>
       </c>
       <c r="M353" s="6" t="s">
-        <v>5188</v>
+        <v>5186</v>
       </c>
       <c r="N353" s="2" t="s">
         <v>25</v>
@@ -33492,7 +33552,7 @@
         <v>2213</v>
       </c>
       <c r="H354" s="7" t="s">
-        <v>5190</v>
+        <v>5188</v>
       </c>
       <c r="I354" s="8" t="s">
         <v>2116</v>
@@ -33501,7 +33561,7 @@
         <v>2117</v>
       </c>
       <c r="K354" s="8" t="s">
-        <v>5191</v>
+        <v>5189</v>
       </c>
       <c r="L354" s="4" t="s">
         <v>32</v>
@@ -33627,13 +33687,13 @@
         <v>2230</v>
       </c>
       <c r="K357" s="6" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="L357" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M357" s="6" t="s">
-        <v>5136</v>
+        <v>5134</v>
       </c>
       <c r="N357" s="2" t="s">
         <v>25</v>
@@ -33660,13 +33720,13 @@
         <v>2232</v>
       </c>
       <c r="H358" s="8" t="s">
-        <v>5194</v>
+        <v>5192</v>
       </c>
       <c r="I358" s="8" t="s">
-        <v>5192</v>
+        <v>5190</v>
       </c>
       <c r="J358" s="8" t="s">
-        <v>5193</v>
+        <v>5191</v>
       </c>
       <c r="K358" s="8" t="s">
         <v>1453</v>
@@ -33675,7 +33735,7 @@
         <v>23</v>
       </c>
       <c r="M358" s="6" t="s">
-        <v>5195</v>
+        <v>5193</v>
       </c>
       <c r="N358" s="2" t="s">
         <v>25</v>
@@ -33699,16 +33759,16 @@
         <v>358</v>
       </c>
       <c r="G359" s="6" t="s">
+        <v>5194</v>
+      </c>
+      <c r="H359" s="8" t="s">
+        <v>5197</v>
+      </c>
+      <c r="I359" s="8" t="s">
+        <v>5195</v>
+      </c>
+      <c r="J359" s="8" t="s">
         <v>5196</v>
-      </c>
-      <c r="H359" s="8" t="s">
-        <v>5199</v>
-      </c>
-      <c r="I359" s="8" t="s">
-        <v>5197</v>
-      </c>
-      <c r="J359" s="8" t="s">
-        <v>5198</v>
       </c>
       <c r="K359" s="8" t="s">
         <v>1453</v>
@@ -33717,7 +33777,7 @@
         <v>23</v>
       </c>
       <c r="M359" s="6" t="s">
-        <v>5200</v>
+        <v>5198</v>
       </c>
       <c r="N359" s="2" t="s">
         <v>25</v>
@@ -33741,28 +33801,28 @@
         <v>359</v>
       </c>
       <c r="G360" s="10" t="s">
+        <v>5199</v>
+      </c>
+      <c r="H360" s="10" t="s">
+        <v>5200</v>
+      </c>
+      <c r="I360" s="10" t="s">
         <v>5201</v>
       </c>
-      <c r="H360" s="10" t="s">
+      <c r="J360" s="10" t="s">
         <v>5202</v>
       </c>
-      <c r="I360" s="10" t="s">
-        <v>5203</v>
-      </c>
-      <c r="J360" s="10" t="s">
-        <v>5204</v>
-      </c>
       <c r="K360" s="10" t="s">
-        <v>5181</v>
+        <v>5179</v>
       </c>
       <c r="L360" s="11" t="s">
         <v>23</v>
       </c>
       <c r="M360" s="10" t="s">
-        <v>5205</v>
+        <v>5203</v>
       </c>
       <c r="N360" s="10" t="s">
-        <v>5183</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="361" spans="1:14" ht="27.6">
@@ -33843,7 +33903,7 @@
         <v>47</v>
       </c>
       <c r="M362" s="6" t="s">
-        <v>5206</v>
+        <v>5204</v>
       </c>
       <c r="N362" s="2" t="s">
         <v>25</v>
@@ -33870,10 +33930,10 @@
         <v>2241</v>
       </c>
       <c r="H363" t="s">
-        <v>5207</v>
+        <v>5205</v>
       </c>
       <c r="I363" s="8" t="s">
-        <v>5208</v>
+        <v>5206</v>
       </c>
       <c r="J363" s="2" t="s">
         <v>2242</v>
@@ -33882,10 +33942,10 @@
         <v>2243</v>
       </c>
       <c r="L363" s="4" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="M363" s="6" t="s">
-        <v>5209</v>
+        <v>5207</v>
       </c>
       <c r="N363" s="2" t="s">
         <v>25</v>
@@ -42939,7 +42999,7 @@
         <v>201</v>
       </c>
       <c r="G579" s="6" t="s">
-        <v>5252</v>
+        <v>5250</v>
       </c>
       <c r="H579" s="2" t="s">
         <v>3618</v>
@@ -42951,13 +43011,13 @@
         <v>3620</v>
       </c>
       <c r="K579" s="2" t="s">
-        <v>5256</v>
+        <v>5254</v>
       </c>
       <c r="L579" s="4" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="M579" s="6" t="s">
-        <v>5257</v>
+        <v>5255</v>
       </c>
       <c r="N579" s="2" t="s">
         <v>25</v>
@@ -43533,19 +43593,19 @@
         <v>3706</v>
       </c>
       <c r="I593" s="2" t="s">
-        <v>5255</v>
+        <v>5253</v>
       </c>
       <c r="J593" s="2" t="s">
         <v>3707</v>
       </c>
       <c r="K593" s="2" t="s">
-        <v>5254</v>
+        <v>5252</v>
       </c>
       <c r="L593" s="4" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="M593" s="6" t="s">
-        <v>5253</v>
+        <v>5251</v>
       </c>
       <c r="N593" s="2" t="s">
         <v>25</v>
@@ -45183,7 +45243,7 @@
         <v>23</v>
       </c>
       <c r="M632" s="6" t="s">
-        <v>5210</v>
+        <v>5208</v>
       </c>
       <c r="N632" s="2" t="s">
         <v>25</v>
@@ -45339,19 +45399,19 @@
         <v>3939</v>
       </c>
       <c r="I636" s="8" t="s">
+        <v>5209</v>
+      </c>
+      <c r="J636" s="8" t="s">
         <v>5211</v>
       </c>
-      <c r="J636" s="8" t="s">
-        <v>5213</v>
-      </c>
       <c r="K636" s="8" t="s">
-        <v>5212</v>
+        <v>5210</v>
       </c>
       <c r="L636" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M636" s="6" t="s">
-        <v>5214</v>
+        <v>5212</v>
       </c>
       <c r="N636" s="2" t="s">
         <v>25</v>
@@ -45513,13 +45573,13 @@
         <v>3963</v>
       </c>
       <c r="K640" s="7" t="s">
-        <v>5215</v>
+        <v>5213</v>
       </c>
       <c r="L640" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M640" s="6" t="s">
-        <v>5216</v>
+        <v>5214</v>
       </c>
       <c r="N640" s="2" t="s">
         <v>25</v>
@@ -45714,22 +45774,22 @@
         <v>3991</v>
       </c>
       <c r="H645" s="8" t="s">
-        <v>5217</v>
+        <v>5215</v>
       </c>
       <c r="I645" s="8" t="s">
         <v>4047</v>
       </c>
       <c r="J645" s="8" t="s">
-        <v>5218</v>
+        <v>5216</v>
       </c>
       <c r="K645" s="8" t="s">
-        <v>5219</v>
+        <v>5217</v>
       </c>
       <c r="L645" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M645" s="6" t="s">
-        <v>5220</v>
+        <v>5218</v>
       </c>
       <c r="N645" s="2" t="s">
         <v>25</v>
@@ -45753,7 +45813,7 @@
         <v>268</v>
       </c>
       <c r="G646" s="2" t="s">
-        <v>5221</v>
+        <v>5219</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>3086</v>
@@ -45765,7 +45825,7 @@
         <v>3993</v>
       </c>
       <c r="K646" s="7" t="s">
-        <v>5132</v>
+        <v>5130</v>
       </c>
       <c r="L646" s="4" t="s">
         <v>23</v>
@@ -45795,28 +45855,28 @@
         <v>269</v>
       </c>
       <c r="G647" s="15" t="s">
+        <v>5220</v>
+      </c>
+      <c r="H647" s="15" t="s">
+        <v>5221</v>
+      </c>
+      <c r="I647" s="15" t="s">
         <v>5222</v>
       </c>
-      <c r="H647" s="15" t="s">
+      <c r="J647" s="15" t="s">
         <v>5223</v>
       </c>
-      <c r="I647" s="15" t="s">
+      <c r="K647" s="15" t="s">
         <v>5224</v>
-      </c>
-      <c r="J647" s="15" t="s">
-        <v>5225</v>
-      </c>
-      <c r="K647" s="15" t="s">
-        <v>5226</v>
       </c>
       <c r="L647" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M647" s="17" t="s">
-        <v>5227</v>
+        <v>5225</v>
       </c>
       <c r="N647" s="15" t="s">
-        <v>5228</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="648" spans="1:14" ht="27.6">
@@ -45921,7 +45981,7 @@
         <v>272</v>
       </c>
       <c r="G650" s="7" t="s">
-        <v>5229</v>
+        <v>5227</v>
       </c>
       <c r="H650" s="2" t="s">
         <v>4011</v>
@@ -45939,7 +45999,7 @@
         <v>32</v>
       </c>
       <c r="M650" s="6" t="s">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="N650" s="2" t="s">
         <v>25</v>
@@ -45981,7 +46041,7 @@
         <v>23</v>
       </c>
       <c r="M651" s="6" t="s">
-        <v>5231</v>
+        <v>5229</v>
       </c>
       <c r="N651" s="2" t="s">
         <v>25</v>
@@ -46023,7 +46083,7 @@
         <v>55</v>
       </c>
       <c r="M652" s="6" t="s">
-        <v>5232</v>
+        <v>5230</v>
       </c>
       <c r="N652" s="2" t="s">
         <v>25</v>
@@ -46059,13 +46119,13 @@
         <v>4030</v>
       </c>
       <c r="K653" s="6" t="s">
-        <v>5234</v>
+        <v>5232</v>
       </c>
       <c r="L653" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M653" s="6" t="s">
-        <v>5233</v>
+        <v>5231</v>
       </c>
       <c r="N653" s="2" t="s">
         <v>25</v>
@@ -46107,7 +46167,7 @@
         <v>47</v>
       </c>
       <c r="M654" s="6" t="s">
-        <v>5235</v>
+        <v>5233</v>
       </c>
       <c r="N654" s="2" t="s">
         <v>25</v>
@@ -46149,7 +46209,7 @@
         <v>47</v>
       </c>
       <c r="M655" s="6" t="s">
-        <v>5236</v>
+        <v>5234</v>
       </c>
       <c r="N655" s="2" t="s">
         <v>25</v>
@@ -46191,7 +46251,7 @@
         <v>47</v>
       </c>
       <c r="M656" s="6" t="s">
-        <v>5237</v>
+        <v>5235</v>
       </c>
       <c r="N656" s="2" t="s">
         <v>25</v>
@@ -46227,13 +46287,13 @@
         <v>4052</v>
       </c>
       <c r="K657" s="7" t="s">
-        <v>5238</v>
+        <v>5236</v>
       </c>
       <c r="L657" s="4" t="s">
         <v>23</v>
       </c>
       <c r="M657" s="6" t="s">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="N657" s="2" t="s">
         <v>25</v>
@@ -46275,7 +46335,7 @@
         <v>47</v>
       </c>
       <c r="M658" s="6" t="s">
-        <v>5240</v>
+        <v>5238</v>
       </c>
       <c r="N658" s="2" t="s">
         <v>25</v>
@@ -46317,7 +46377,7 @@
         <v>32</v>
       </c>
       <c r="M659" s="6" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="N659" s="2" t="s">
         <v>25</v>
@@ -46359,7 +46419,7 @@
         <v>23</v>
       </c>
       <c r="M660" s="6" t="s">
-        <v>5242</v>
+        <v>5240</v>
       </c>
       <c r="N660" s="2" t="s">
         <v>25</v>
@@ -46401,7 +46461,7 @@
         <v>23</v>
       </c>
       <c r="M661" s="6" t="s">
-        <v>5243</v>
+        <v>5241</v>
       </c>
       <c r="N661" s="2" t="s">
         <v>25</v>
@@ -46437,13 +46497,13 @@
         <v>4078</v>
       </c>
       <c r="K662" s="6" t="s">
-        <v>5244</v>
+        <v>5242</v>
       </c>
       <c r="L662" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M662" s="6" t="s">
-        <v>5245</v>
+        <v>5243</v>
       </c>
       <c r="N662" s="2" t="s">
         <v>25</v>
@@ -46485,7 +46545,7 @@
         <v>55</v>
       </c>
       <c r="M663" s="6" t="s">
-        <v>5246</v>
+        <v>5244</v>
       </c>
       <c r="N663" s="2" t="s">
         <v>25</v>
@@ -46518,16 +46578,16 @@
         <v>4088</v>
       </c>
       <c r="J664" s="8" t="s">
-        <v>5248</v>
+        <v>5246</v>
       </c>
       <c r="K664" s="8" t="s">
-        <v>5249</v>
+        <v>5247</v>
       </c>
       <c r="L664" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M664" s="6" t="s">
-        <v>5247</v>
+        <v>5245</v>
       </c>
       <c r="N664" s="2" t="s">
         <v>25</v>
@@ -46569,7 +46629,7 @@
         <v>32</v>
       </c>
       <c r="M665" s="6" t="s">
-        <v>5250</v>
+        <v>5248</v>
       </c>
       <c r="N665" s="2" t="s">
         <v>25</v>
@@ -46611,7 +46671,7 @@
         <v>47</v>
       </c>
       <c r="M666" s="6" t="s">
-        <v>5251</v>
+        <v>5249</v>
       </c>
       <c r="N666" s="2" t="s">
         <v>25</v>
@@ -49829,7 +49889,7 @@
         <v>22</v>
       </c>
       <c r="G742" s="6" t="s">
-        <v>5137</v>
+        <v>5135</v>
       </c>
       <c r="H742" s="2" t="s">
         <v>4584</v>
@@ -50269,7 +50329,7 @@
         <v>32</v>
       </c>
       <c r="G752" s="6" t="s">
-        <v>5138</v>
+        <v>5136</v>
       </c>
       <c r="H752" s="2" t="s">
         <v>4641</v>
@@ -52273,7 +52333,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="798" spans="1:14" ht="69">
+    <row r="798" spans="1:14" ht="28.8">
       <c r="A798" s="3" t="s">
         <v>4954</v>
       </c>
@@ -52292,26 +52352,26 @@
       <c r="F798" s="3">
         <v>28</v>
       </c>
-      <c r="G798" s="2" t="s">
+      <c r="G798" s="6" t="s">
+        <v>5256</v>
+      </c>
+      <c r="H798" s="2" t="s">
         <v>4955</v>
       </c>
-      <c r="H798" s="2" t="s">
+      <c r="I798" s="2" t="s">
         <v>4956</v>
       </c>
-      <c r="I798" s="2" t="s">
+      <c r="J798" s="2" t="s">
         <v>4957</v>
       </c>
-      <c r="J798" s="2" t="s">
+      <c r="K798" s="2" t="s">
         <v>4958</v>
-      </c>
-      <c r="K798" s="2" t="s">
-        <v>4959</v>
       </c>
       <c r="L798" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M798" s="2" t="s">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="N798" s="2" t="s">
         <v>4445</v>
@@ -52319,7 +52379,7 @@
     </row>
     <row r="799" spans="1:14" ht="27.6">
       <c r="A799" s="3" t="s">
-        <v>4961</v>
+        <v>4960</v>
       </c>
       <c r="B799" s="3" t="s">
         <v>15</v>
@@ -52337,25 +52397,25 @@
         <v>29</v>
       </c>
       <c r="G799" s="2" t="s">
+        <v>4961</v>
+      </c>
+      <c r="H799" s="2" t="s">
         <v>4962</v>
       </c>
-      <c r="H799" s="2" t="s">
+      <c r="I799" s="2" t="s">
         <v>4963</v>
       </c>
-      <c r="I799" s="2" t="s">
+      <c r="J799" s="2" t="s">
         <v>4964</v>
       </c>
-      <c r="J799" s="2" t="s">
+      <c r="K799" s="2" t="s">
         <v>4965</v>
-      </c>
-      <c r="K799" s="2" t="s">
-        <v>4966</v>
       </c>
       <c r="L799" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M799" s="2" t="s">
-        <v>4967</v>
+        <v>4966</v>
       </c>
       <c r="N799" s="2" t="s">
         <v>4445</v>
@@ -52363,7 +52423,7 @@
     </row>
     <row r="800" spans="1:14" ht="41.4">
       <c r="A800" s="3" t="s">
-        <v>4968</v>
+        <v>4967</v>
       </c>
       <c r="B800" s="3" t="s">
         <v>15</v>
@@ -52381,25 +52441,25 @@
         <v>30</v>
       </c>
       <c r="G800" s="2" t="s">
+        <v>4968</v>
+      </c>
+      <c r="H800" s="2" t="s">
         <v>4969</v>
       </c>
-      <c r="H800" s="2" t="s">
+      <c r="I800" s="2" t="s">
         <v>4970</v>
       </c>
-      <c r="I800" s="2" t="s">
+      <c r="J800" s="2" t="s">
         <v>4971</v>
       </c>
-      <c r="J800" s="2" t="s">
+      <c r="K800" s="2" t="s">
         <v>4972</v>
-      </c>
-      <c r="K800" s="2" t="s">
-        <v>4973</v>
       </c>
       <c r="L800" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M800" s="2" t="s">
-        <v>4974</v>
+        <v>4973</v>
       </c>
       <c r="N800" s="2" t="s">
         <v>4445</v>
@@ -52407,7 +52467,7 @@
     </row>
     <row r="801" spans="1:14" ht="55.2">
       <c r="A801" s="3" t="s">
-        <v>4975</v>
+        <v>4974</v>
       </c>
       <c r="B801" s="3" t="s">
         <v>15</v>
@@ -52425,25 +52485,25 @@
         <v>31</v>
       </c>
       <c r="G801" s="2" t="s">
+        <v>4975</v>
+      </c>
+      <c r="H801" s="2" t="s">
         <v>4976</v>
       </c>
-      <c r="H801" s="2" t="s">
+      <c r="I801" s="2" t="s">
         <v>4977</v>
       </c>
-      <c r="I801" s="2" t="s">
+      <c r="J801" s="2" t="s">
         <v>4978</v>
       </c>
-      <c r="J801" s="2" t="s">
+      <c r="K801" s="2" t="s">
         <v>4979</v>
-      </c>
-      <c r="K801" s="2" t="s">
-        <v>4980</v>
       </c>
       <c r="L801" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M801" s="2" t="s">
-        <v>4981</v>
+        <v>4980</v>
       </c>
       <c r="N801" s="2" t="s">
         <v>4445</v>
@@ -52451,7 +52511,7 @@
     </row>
     <row r="802" spans="1:14" ht="41.4">
       <c r="A802" s="3" t="s">
-        <v>4982</v>
+        <v>4981</v>
       </c>
       <c r="B802" s="3" t="s">
         <v>15</v>
@@ -52469,25 +52529,25 @@
         <v>32</v>
       </c>
       <c r="G802" s="2" t="s">
+        <v>4982</v>
+      </c>
+      <c r="H802" s="2" t="s">
         <v>4983</v>
       </c>
-      <c r="H802" s="2" t="s">
+      <c r="I802" s="2" t="s">
         <v>4984</v>
       </c>
-      <c r="I802" s="2" t="s">
+      <c r="J802" s="2" t="s">
         <v>4985</v>
       </c>
-      <c r="J802" s="2" t="s">
+      <c r="K802" s="2" t="s">
         <v>4986</v>
-      </c>
-      <c r="K802" s="2" t="s">
-        <v>4987</v>
       </c>
       <c r="L802" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M802" s="2" t="s">
-        <v>4988</v>
+        <v>4987</v>
       </c>
       <c r="N802" s="2" t="s">
         <v>4445</v>
@@ -52495,7 +52555,7 @@
     </row>
     <row r="803" spans="1:14" ht="41.4">
       <c r="A803" s="3" t="s">
-        <v>4989</v>
+        <v>4988</v>
       </c>
       <c r="B803" s="3" t="s">
         <v>15</v>
@@ -52513,25 +52573,25 @@
         <v>33</v>
       </c>
       <c r="G803" s="2" t="s">
+        <v>4989</v>
+      </c>
+      <c r="H803" s="2" t="s">
         <v>4990</v>
       </c>
-      <c r="H803" s="2" t="s">
+      <c r="I803" s="2" t="s">
         <v>4991</v>
       </c>
-      <c r="I803" s="2" t="s">
+      <c r="J803" s="2" t="s">
         <v>4992</v>
       </c>
-      <c r="J803" s="2" t="s">
+      <c r="K803" s="2" t="s">
         <v>4993</v>
-      </c>
-      <c r="K803" s="2" t="s">
-        <v>4994</v>
       </c>
       <c r="L803" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M803" s="2" t="s">
-        <v>4995</v>
+        <v>4994</v>
       </c>
       <c r="N803" s="2" t="s">
         <v>4445</v>
@@ -52539,7 +52599,7 @@
     </row>
     <row r="804" spans="1:14" ht="27.6">
       <c r="A804" s="3" t="s">
-        <v>4996</v>
+        <v>4995</v>
       </c>
       <c r="B804" s="3" t="s">
         <v>15</v>
@@ -52557,25 +52617,25 @@
         <v>34</v>
       </c>
       <c r="G804" s="2" t="s">
+        <v>4996</v>
+      </c>
+      <c r="H804" s="2" t="s">
         <v>4997</v>
       </c>
-      <c r="H804" s="2" t="s">
+      <c r="I804" s="2" t="s">
         <v>4998</v>
       </c>
-      <c r="I804" s="2" t="s">
+      <c r="J804" s="2" t="s">
         <v>4999</v>
       </c>
-      <c r="J804" s="2" t="s">
+      <c r="K804" s="2" t="s">
         <v>5000</v>
-      </c>
-      <c r="K804" s="2" t="s">
-        <v>5001</v>
       </c>
       <c r="L804" s="4" t="s">
         <v>23</v>
       </c>
       <c r="M804" s="2" t="s">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="N804" s="2" t="s">
         <v>4445</v>
@@ -52583,7 +52643,7 @@
     </row>
     <row r="805" spans="1:14" ht="27.6">
       <c r="A805" s="3" t="s">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="B805" s="3" t="s">
         <v>15</v>
@@ -52601,25 +52661,25 @@
         <v>35</v>
       </c>
       <c r="G805" s="2" t="s">
+        <v>5003</v>
+      </c>
+      <c r="H805" s="2" t="s">
         <v>5004</v>
       </c>
-      <c r="H805" s="2" t="s">
+      <c r="I805" s="2" t="s">
         <v>5005</v>
       </c>
-      <c r="I805" s="2" t="s">
+      <c r="J805" s="2" t="s">
         <v>5006</v>
       </c>
-      <c r="J805" s="2" t="s">
+      <c r="K805" s="2" t="s">
         <v>5007</v>
-      </c>
-      <c r="K805" s="2" t="s">
-        <v>5008</v>
       </c>
       <c r="L805" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M805" s="2" t="s">
-        <v>5009</v>
+        <v>5008</v>
       </c>
       <c r="N805" s="2" t="s">
         <v>4445</v>
@@ -52627,7 +52687,7 @@
     </row>
     <row r="806" spans="1:14" ht="55.2">
       <c r="A806" s="3" t="s">
-        <v>5010</v>
+        <v>5009</v>
       </c>
       <c r="B806" s="3" t="s">
         <v>15</v>
@@ -52645,25 +52705,25 @@
         <v>36</v>
       </c>
       <c r="G806" s="2" t="s">
+        <v>5010</v>
+      </c>
+      <c r="H806" s="2" t="s">
         <v>5011</v>
       </c>
-      <c r="H806" s="2" t="s">
+      <c r="I806" s="2" t="s">
         <v>5012</v>
       </c>
-      <c r="I806" s="2" t="s">
+      <c r="J806" s="2" t="s">
         <v>5013</v>
       </c>
-      <c r="J806" s="2" t="s">
+      <c r="K806" s="2" t="s">
         <v>5014</v>
-      </c>
-      <c r="K806" s="2" t="s">
-        <v>5015</v>
       </c>
       <c r="L806" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M806" s="2" t="s">
-        <v>5016</v>
+        <v>5015</v>
       </c>
       <c r="N806" s="2" t="s">
         <v>4445</v>
@@ -52671,7 +52731,7 @@
     </row>
     <row r="807" spans="1:14" ht="55.2">
       <c r="A807" s="3" t="s">
-        <v>5017</v>
+        <v>5016</v>
       </c>
       <c r="B807" s="3" t="s">
         <v>15</v>
@@ -52689,7 +52749,7 @@
         <v>37</v>
       </c>
       <c r="G807" s="2" t="s">
-        <v>5018</v>
+        <v>5017</v>
       </c>
       <c r="H807" s="2" t="s">
         <v>555</v>
@@ -52707,7 +52767,7 @@
         <v>47</v>
       </c>
       <c r="M807" s="2" t="s">
-        <v>5019</v>
+        <v>5018</v>
       </c>
       <c r="N807" s="2" t="s">
         <v>4445</v>
@@ -52715,7 +52775,7 @@
     </row>
     <row r="808" spans="1:14" ht="27.6">
       <c r="A808" s="3" t="s">
-        <v>5020</v>
+        <v>5019</v>
       </c>
       <c r="B808" s="3" t="s">
         <v>15</v>
@@ -52733,25 +52793,25 @@
         <v>38</v>
       </c>
       <c r="G808" s="2" t="s">
+        <v>5020</v>
+      </c>
+      <c r="H808" s="2" t="s">
         <v>5021</v>
       </c>
-      <c r="H808" s="2" t="s">
+      <c r="I808" s="2" t="s">
         <v>5022</v>
       </c>
-      <c r="I808" s="2" t="s">
+      <c r="J808" s="2" t="s">
         <v>5023</v>
       </c>
-      <c r="J808" s="2" t="s">
+      <c r="K808" s="2" t="s">
         <v>5024</v>
-      </c>
-      <c r="K808" s="2" t="s">
-        <v>5025</v>
       </c>
       <c r="L808" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M808" s="2" t="s">
-        <v>5026</v>
+        <v>5025</v>
       </c>
       <c r="N808" s="2" t="s">
         <v>4445</v>
@@ -52759,7 +52819,7 @@
     </row>
     <row r="809" spans="1:14" ht="55.2">
       <c r="A809" s="3" t="s">
-        <v>5027</v>
+        <v>5026</v>
       </c>
       <c r="B809" s="3" t="s">
         <v>15</v>
@@ -52777,25 +52837,25 @@
         <v>39</v>
       </c>
       <c r="G809" s="2" t="s">
+        <v>5027</v>
+      </c>
+      <c r="H809" s="2" t="s">
         <v>5028</v>
       </c>
-      <c r="H809" s="2" t="s">
+      <c r="I809" s="2" t="s">
         <v>5029</v>
       </c>
-      <c r="I809" s="2" t="s">
+      <c r="J809" s="2" t="s">
         <v>5030</v>
       </c>
-      <c r="J809" s="2" t="s">
+      <c r="K809" s="2" t="s">
         <v>5031</v>
-      </c>
-      <c r="K809" s="2" t="s">
-        <v>5032</v>
       </c>
       <c r="L809" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M809" s="2" t="s">
-        <v>5033</v>
+        <v>5032</v>
       </c>
       <c r="N809" s="2" t="s">
         <v>4445</v>
@@ -52803,7 +52863,7 @@
     </row>
     <row r="810" spans="1:14">
       <c r="A810" s="3" t="s">
-        <v>5034</v>
+        <v>5033</v>
       </c>
       <c r="B810" s="3" t="s">
         <v>15</v>
@@ -52821,16 +52881,16 @@
         <v>40</v>
       </c>
       <c r="G810" s="2" t="s">
+        <v>5034</v>
+      </c>
+      <c r="H810" s="2" t="s">
         <v>5035</v>
       </c>
-      <c r="H810" s="2" t="s">
+      <c r="I810" s="2" t="s">
         <v>5036</v>
       </c>
-      <c r="I810" s="2" t="s">
+      <c r="J810" s="2" t="s">
         <v>5037</v>
-      </c>
-      <c r="J810" s="2" t="s">
-        <v>5038</v>
       </c>
       <c r="K810" s="2" t="s">
         <v>3607</v>
@@ -52839,7 +52899,7 @@
         <v>55</v>
       </c>
       <c r="M810" s="2" t="s">
-        <v>5039</v>
+        <v>5038</v>
       </c>
       <c r="N810" s="2" t="s">
         <v>4445</v>
@@ -52847,7 +52907,7 @@
     </row>
     <row r="811" spans="1:14" ht="41.4">
       <c r="A811" s="3" t="s">
-        <v>5040</v>
+        <v>5039</v>
       </c>
       <c r="B811" s="3" t="s">
         <v>15</v>
@@ -52865,25 +52925,25 @@
         <v>41</v>
       </c>
       <c r="G811" s="2" t="s">
+        <v>5040</v>
+      </c>
+      <c r="H811" s="2" t="s">
         <v>5041</v>
       </c>
-      <c r="H811" s="2" t="s">
+      <c r="I811" s="2" t="s">
         <v>5042</v>
       </c>
-      <c r="I811" s="2" t="s">
+      <c r="J811" s="2" t="s">
         <v>5043</v>
       </c>
-      <c r="J811" s="2" t="s">
+      <c r="K811" s="2" t="s">
         <v>5044</v>
-      </c>
-      <c r="K811" s="2" t="s">
-        <v>5045</v>
       </c>
       <c r="L811" s="4" t="s">
         <v>23</v>
       </c>
       <c r="M811" s="2" t="s">
-        <v>5046</v>
+        <v>5045</v>
       </c>
       <c r="N811" s="2" t="s">
         <v>4445</v>
@@ -52891,7 +52951,7 @@
     </row>
     <row r="812" spans="1:14" ht="55.2">
       <c r="A812" s="3" t="s">
-        <v>5047</v>
+        <v>5046</v>
       </c>
       <c r="B812" s="3" t="s">
         <v>15</v>
@@ -52909,25 +52969,25 @@
         <v>42</v>
       </c>
       <c r="G812" s="2" t="s">
+        <v>5047</v>
+      </c>
+      <c r="H812" s="2" t="s">
         <v>5048</v>
       </c>
-      <c r="H812" s="2" t="s">
+      <c r="I812" s="2" t="s">
         <v>5049</v>
-      </c>
-      <c r="I812" s="2" t="s">
-        <v>5050</v>
       </c>
       <c r="J812" s="2" t="s">
         <v>2749</v>
       </c>
       <c r="K812" s="2" t="s">
-        <v>5051</v>
+        <v>5050</v>
       </c>
       <c r="L812" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M812" s="2" t="s">
-        <v>5052</v>
+        <v>5051</v>
       </c>
       <c r="N812" s="2" t="s">
         <v>4445</v>
@@ -52935,7 +52995,7 @@
     </row>
     <row r="813" spans="1:14" ht="27.6">
       <c r="A813" s="3" t="s">
-        <v>5053</v>
+        <v>5052</v>
       </c>
       <c r="B813" s="3" t="s">
         <v>15</v>
@@ -52953,33 +53013,33 @@
         <v>43</v>
       </c>
       <c r="G813" s="2" t="s">
+        <v>5053</v>
+      </c>
+      <c r="H813" s="2" t="s">
         <v>5054</v>
       </c>
-      <c r="H813" s="2" t="s">
+      <c r="I813" s="2" t="s">
         <v>5055</v>
       </c>
-      <c r="I813" s="2" t="s">
+      <c r="J813" s="2" t="s">
         <v>5056</v>
       </c>
-      <c r="J813" s="2" t="s">
+      <c r="K813" s="2" t="s">
         <v>5057</v>
-      </c>
-      <c r="K813" s="2" t="s">
-        <v>5058</v>
       </c>
       <c r="L813" s="4" t="s">
         <v>23</v>
       </c>
       <c r="M813" s="2" t="s">
-        <v>5059</v>
+        <v>5058</v>
       </c>
       <c r="N813" s="2" t="s">
         <v>4445</v>
       </c>
     </row>
-    <row r="814" spans="1:14" ht="82.8">
+    <row r="814" spans="1:14" ht="43.2">
       <c r="A814" s="3" t="s">
-        <v>5060</v>
+        <v>5059</v>
       </c>
       <c r="B814" s="3" t="s">
         <v>15</v>
@@ -52996,26 +53056,26 @@
       <c r="F814" s="3">
         <v>44</v>
       </c>
-      <c r="G814" s="2" t="s">
+      <c r="G814" s="6" t="s">
+        <v>5257</v>
+      </c>
+      <c r="H814" s="2" t="s">
+        <v>5060</v>
+      </c>
+      <c r="I814" s="2" t="s">
         <v>5061</v>
       </c>
-      <c r="H814" s="2" t="s">
+      <c r="J814" s="2" t="s">
         <v>5062</v>
       </c>
-      <c r="I814" s="2" t="s">
+      <c r="K814" s="2" t="s">
         <v>5063</v>
-      </c>
-      <c r="J814" s="2" t="s">
-        <v>5064</v>
-      </c>
-      <c r="K814" s="2" t="s">
-        <v>5065</v>
       </c>
       <c r="L814" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M814" s="2" t="s">
-        <v>5066</v>
+        <v>5064</v>
       </c>
       <c r="N814" s="2" t="s">
         <v>4445</v>
@@ -53023,7 +53083,7 @@
     </row>
     <row r="815" spans="1:14" ht="27.6">
       <c r="A815" s="3" t="s">
-        <v>5067</v>
+        <v>5065</v>
       </c>
       <c r="B815" s="3" t="s">
         <v>15</v>
@@ -53041,25 +53101,25 @@
         <v>45</v>
       </c>
       <c r="G815" s="2" t="s">
+        <v>5066</v>
+      </c>
+      <c r="H815" s="2" t="s">
+        <v>5067</v>
+      </c>
+      <c r="I815" s="2" t="s">
         <v>5068</v>
       </c>
-      <c r="H815" s="2" t="s">
+      <c r="J815" s="2" t="s">
         <v>5069</v>
       </c>
-      <c r="I815" s="2" t="s">
+      <c r="K815" s="2" t="s">
         <v>5070</v>
-      </c>
-      <c r="J815" s="2" t="s">
-        <v>5071</v>
-      </c>
-      <c r="K815" s="2" t="s">
-        <v>5072</v>
       </c>
       <c r="L815" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M815" s="2" t="s">
-        <v>5073</v>
+        <v>5071</v>
       </c>
       <c r="N815" s="2" t="s">
         <v>4445</v>
@@ -53067,7 +53127,7 @@
     </row>
     <row r="816" spans="1:14">
       <c r="A816" s="3" t="s">
-        <v>5074</v>
+        <v>5072</v>
       </c>
       <c r="B816" s="3" t="s">
         <v>15</v>
@@ -53085,25 +53145,25 @@
         <v>46</v>
       </c>
       <c r="G816" s="2" t="s">
+        <v>5073</v>
+      </c>
+      <c r="H816" s="2" t="s">
+        <v>5074</v>
+      </c>
+      <c r="I816" s="2" t="s">
         <v>5075</v>
       </c>
-      <c r="H816" s="2" t="s">
+      <c r="J816" s="2" t="s">
         <v>5076</v>
       </c>
-      <c r="I816" s="2" t="s">
+      <c r="K816" s="2" t="s">
         <v>5077</v>
-      </c>
-      <c r="J816" s="2" t="s">
-        <v>5078</v>
-      </c>
-      <c r="K816" s="2" t="s">
-        <v>5079</v>
       </c>
       <c r="L816" s="4" t="s">
         <v>23</v>
       </c>
       <c r="M816" s="2" t="s">
-        <v>5080</v>
+        <v>5078</v>
       </c>
       <c r="N816" s="2" t="s">
         <v>4445</v>
@@ -53111,7 +53171,7 @@
     </row>
     <row r="817" spans="1:14" ht="27.6">
       <c r="A817" s="3" t="s">
-        <v>5081</v>
+        <v>5079</v>
       </c>
       <c r="B817" s="3" t="s">
         <v>15</v>
@@ -53129,25 +53189,25 @@
         <v>47</v>
       </c>
       <c r="G817" s="2" t="s">
+        <v>5080</v>
+      </c>
+      <c r="H817" s="2" t="s">
+        <v>5081</v>
+      </c>
+      <c r="I817" s="2" t="s">
         <v>5082</v>
       </c>
-      <c r="H817" s="2" t="s">
+      <c r="J817" s="2" t="s">
         <v>5083</v>
       </c>
-      <c r="I817" s="2" t="s">
+      <c r="K817" s="2" t="s">
         <v>5084</v>
-      </c>
-      <c r="J817" s="2" t="s">
-        <v>5085</v>
-      </c>
-      <c r="K817" s="2" t="s">
-        <v>5086</v>
       </c>
       <c r="L817" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M817" s="2" t="s">
-        <v>5087</v>
+        <v>5085</v>
       </c>
       <c r="N817" s="2" t="s">
         <v>4445</v>
@@ -53155,7 +53215,7 @@
     </row>
     <row r="818" spans="1:14">
       <c r="A818" s="3" t="s">
-        <v>5088</v>
+        <v>5086</v>
       </c>
       <c r="B818" s="3" t="s">
         <v>15</v>
@@ -53173,25 +53233,25 @@
         <v>48</v>
       </c>
       <c r="G818" s="2" t="s">
+        <v>5087</v>
+      </c>
+      <c r="H818" s="2" t="s">
+        <v>5088</v>
+      </c>
+      <c r="I818" s="2" t="s">
         <v>5089</v>
       </c>
-      <c r="H818" s="2" t="s">
+      <c r="J818" s="2" t="s">
         <v>5090</v>
       </c>
-      <c r="I818" s="2" t="s">
+      <c r="K818" s="2" t="s">
         <v>5091</v>
-      </c>
-      <c r="J818" s="2" t="s">
-        <v>5092</v>
-      </c>
-      <c r="K818" s="2" t="s">
-        <v>5093</v>
       </c>
       <c r="L818" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M818" s="2" t="s">
-        <v>5094</v>
+        <v>5092</v>
       </c>
       <c r="N818" s="2" t="s">
         <v>4445</v>
@@ -53199,7 +53259,7 @@
     </row>
     <row r="819" spans="1:14" ht="41.4">
       <c r="A819" s="3" t="s">
-        <v>5095</v>
+        <v>5093</v>
       </c>
       <c r="B819" s="3" t="s">
         <v>15</v>
@@ -53217,25 +53277,25 @@
         <v>49</v>
       </c>
       <c r="G819" s="2" t="s">
+        <v>5094</v>
+      </c>
+      <c r="H819" s="2" t="s">
+        <v>5095</v>
+      </c>
+      <c r="I819" s="2" t="s">
         <v>5096</v>
       </c>
-      <c r="H819" s="2" t="s">
+      <c r="J819" s="2" t="s">
         <v>5097</v>
       </c>
-      <c r="I819" s="2" t="s">
+      <c r="K819" s="2" t="s">
         <v>5098</v>
-      </c>
-      <c r="J819" s="2" t="s">
-        <v>5099</v>
-      </c>
-      <c r="K819" s="2" t="s">
-        <v>5100</v>
       </c>
       <c r="L819" s="4" t="s">
         <v>47</v>
       </c>
       <c r="M819" s="2" t="s">
-        <v>5101</v>
+        <v>5099</v>
       </c>
       <c r="N819" s="2" t="s">
         <v>4445</v>
@@ -53243,7 +53303,7 @@
     </row>
     <row r="820" spans="1:14" ht="27.6">
       <c r="A820" s="3" t="s">
-        <v>5102</v>
+        <v>5100</v>
       </c>
       <c r="B820" s="3" t="s">
         <v>15</v>
@@ -53261,16 +53321,16 @@
         <v>50</v>
       </c>
       <c r="G820" s="2" t="s">
+        <v>5101</v>
+      </c>
+      <c r="H820" s="2" t="s">
+        <v>5102</v>
+      </c>
+      <c r="I820" s="2" t="s">
         <v>5103</v>
       </c>
-      <c r="H820" s="2" t="s">
+      <c r="J820" s="2" t="s">
         <v>5104</v>
-      </c>
-      <c r="I820" s="2" t="s">
-        <v>5105</v>
-      </c>
-      <c r="J820" s="2" t="s">
-        <v>5106</v>
       </c>
       <c r="K820" s="2" t="s">
         <v>3746</v>
@@ -53279,7 +53339,7 @@
         <v>47</v>
       </c>
       <c r="M820" s="2" t="s">
-        <v>5107</v>
+        <v>5105</v>
       </c>
       <c r="N820" s="2" t="s">
         <v>4445</v>
@@ -53324,10 +53384,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>5108</v>
+        <v>5106</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>5109</v>
+        <v>5107</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -53341,7 +53401,7 @@
         <v>427</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5110</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -53355,7 +53415,7 @@
         <v>392</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5111</v>
+        <v>5109</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -53363,27 +53423,27 @@
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5112</v>
+        <v>5110</v>
       </c>
       <c r="C4" s="2">
         <v>819</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5113</v>
+        <v>5111</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>5114</v>
+        <v>5112</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5115</v>
+        <v>5113</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5116</v>
+        <v>5114</v>
       </c>
     </row>
   </sheetData>
@@ -53403,18 +53463,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>5117</v>
+        <v>5115</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>5109</v>
+        <v>5107</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>5118</v>
+        <v>5116</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5119</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -53422,7 +53482,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5120</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -53430,7 +53490,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5121</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -53438,7 +53498,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5122</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -53446,31 +53506,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5123</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>5124</v>
+        <v>5122</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5125</v>
+        <v>5123</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>5126</v>
+        <v>5124</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5127</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>5128</v>
+        <v>5126</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5129</v>
+        <v>5127</v>
       </c>
     </row>
   </sheetData>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NANCY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4020BBE9-159D-4F43-B8B8-2487A383F7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F69E8D-F2DF-45B0-BB63-D03DB21839EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20423,7 +20423,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> A</t>
+      <t xml:space="preserve"> C</t>
     </r>
     <r>
       <rPr>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NANCY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5907ED4C-3D8E-431A-92AE-B4ABE5DB6FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9824D66-E49E-459D-A144-0AE61783CB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NANCY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9824D66-E49E-459D-A144-0AE61783CB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E65E9A2-B1E8-4C80-A5BC-C4C69AC2AF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25039,43 +25039,6 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>公布／題庫答案為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：最終產品處理。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">
-「最終產品處理」屬於第五階段（廢棄處理），不論產品是進入垃圾掩埋場、焚化爐或是進行回收再生，其過程所產生的溫室氣體排放量，都必須完整納入產品的碳足跡總量中。</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
       <t>分別列出但不包括在</t>
     </r>
     <r>
@@ -26363,6 +26326,53 @@
         <charset val="136"/>
       </rPr>
       <t>地區或國家電網的平均排放因數</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>公布／題庫答案為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>以上皆是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>碳足跡採完整的生命週期概念（如搖籃到墳墓），舉凡原料取得、生產製造、產品配送、實際使用到最終產品的廢棄與處理，各階段產生的溫室氣體排放均需納入總量計算中。</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -36110,7 +36120,7 @@
         <v>4938</v>
       </c>
       <c r="M220" s="5" t="s">
-        <v>5239</v>
+        <v>5238</v>
       </c>
       <c r="N220" s="1" t="s">
         <v>24</v>
@@ -37202,7 +37212,7 @@
         <v>4933</v>
       </c>
       <c r="M246" s="5" t="s">
-        <v>5253</v>
+        <v>5252</v>
       </c>
       <c r="N246" s="1" t="s">
         <v>24</v>
@@ -38453,7 +38463,7 @@
         <v>1731</v>
       </c>
       <c r="J276" s="6" t="s">
-        <v>5245</v>
+        <v>5244</v>
       </c>
       <c r="K276" s="1" t="s">
         <v>784</v>
@@ -38462,7 +38472,7 @@
         <v>4930</v>
       </c>
       <c r="M276" s="5" t="s">
-        <v>5246</v>
+        <v>5245</v>
       </c>
       <c r="N276" s="1" t="s">
         <v>24</v>
@@ -38630,7 +38640,7 @@
         <v>4933</v>
       </c>
       <c r="M280" s="5" t="s">
-        <v>5252</v>
+        <v>5251</v>
       </c>
       <c r="N280" s="1" t="s">
         <v>24</v>
@@ -42857,7 +42867,7 @@
         <v>2254</v>
       </c>
       <c r="H381" s="6" t="s">
-        <v>5265</v>
+        <v>5264</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>2255</v>
@@ -42872,7 +42882,7 @@
         <v>4940</v>
       </c>
       <c r="M381" s="5" t="s">
-        <v>5266</v>
+        <v>5265</v>
       </c>
       <c r="N381" s="1" t="s">
         <v>24</v>
@@ -42908,13 +42918,13 @@
         <v>2262</v>
       </c>
       <c r="K382" s="6" t="s">
-        <v>5288</v>
+        <v>5287</v>
       </c>
       <c r="L382" s="3" t="s">
         <v>4938</v>
       </c>
       <c r="M382" s="5" t="s">
-        <v>5289</v>
+        <v>5288</v>
       </c>
       <c r="N382" s="1" t="s">
         <v>24</v>
@@ -43070,7 +43080,7 @@
         <v>2285</v>
       </c>
       <c r="I386" s="6" t="s">
-        <v>5286</v>
+        <v>5285</v>
       </c>
       <c r="J386" s="1" t="s">
         <v>2286</v>
@@ -43082,7 +43092,7 @@
         <v>4933</v>
       </c>
       <c r="M386" s="5" t="s">
-        <v>5287</v>
+        <v>5286</v>
       </c>
       <c r="N386" s="1" t="s">
         <v>24</v>
@@ -44048,7 +44058,7 @@
         <v>4930</v>
       </c>
       <c r="M409" s="5" t="s">
-        <v>5278</v>
+        <v>5277</v>
       </c>
       <c r="N409" s="1" t="s">
         <v>24</v>
@@ -44090,7 +44100,7 @@
         <v>4938</v>
       </c>
       <c r="M410" s="5" t="s">
-        <v>5282</v>
+        <v>5281</v>
       </c>
       <c r="N410" s="1" t="s">
         <v>24</v>
@@ -44705,7 +44715,7 @@
         <v>2536</v>
       </c>
       <c r="H425" s="5" t="s">
-        <v>5250</v>
+        <v>5249</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>2537</v>
@@ -44720,7 +44730,7 @@
         <v>4940</v>
       </c>
       <c r="M425" s="5" t="s">
-        <v>5283</v>
+        <v>5282</v>
       </c>
       <c r="N425" s="1" t="s">
         <v>24</v>
@@ -44747,7 +44757,7 @@
         <v>2541</v>
       </c>
       <c r="H426" s="6" t="s">
-        <v>5247</v>
+        <v>5246</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>2542</v>
@@ -44762,7 +44772,7 @@
         <v>4940</v>
       </c>
       <c r="M426" s="5" t="s">
-        <v>5248</v>
+        <v>5247</v>
       </c>
       <c r="N426" s="1" t="s">
         <v>24</v>
@@ -45131,7 +45141,7 @@
         <v>2597</v>
       </c>
       <c r="J435" s="6" t="s">
-        <v>5271</v>
+        <v>5270</v>
       </c>
       <c r="K435" s="1" t="s">
         <v>2598</v>
@@ -45140,7 +45150,7 @@
         <v>4930</v>
       </c>
       <c r="M435" s="5" t="s">
-        <v>5272</v>
+        <v>5271</v>
       </c>
       <c r="N435" s="1" t="s">
         <v>24</v>
@@ -45167,7 +45177,7 @@
         <v>2600</v>
       </c>
       <c r="H436" s="6" t="s">
-        <v>5279</v>
+        <v>5278</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>2601</v>
@@ -45182,7 +45192,7 @@
         <v>4940</v>
       </c>
       <c r="M436" s="5" t="s">
-        <v>5280</v>
+        <v>5279</v>
       </c>
       <c r="N436" s="1" t="s">
         <v>24</v>
@@ -45299,7 +45309,7 @@
         <v>2621</v>
       </c>
       <c r="J439" s="6" t="s">
-        <v>5241</v>
+        <v>5240</v>
       </c>
       <c r="K439" s="1" t="s">
         <v>2622</v>
@@ -45308,7 +45318,7 @@
         <v>4930</v>
       </c>
       <c r="M439" s="5" t="s">
-        <v>5242</v>
+        <v>5241</v>
       </c>
       <c r="N439" s="1" t="s">
         <v>24</v>
@@ -45671,7 +45681,7 @@
         <v>2678</v>
       </c>
       <c r="H448" s="6" t="s">
-        <v>5260</v>
+        <v>5259</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>2679</v>
@@ -45686,7 +45696,7 @@
         <v>4940</v>
       </c>
       <c r="M448" s="5" t="s">
-        <v>5261</v>
+        <v>5260</v>
       </c>
       <c r="N448" s="1" t="s">
         <v>24</v>
@@ -45800,7 +45810,7 @@
         <v>2626</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>5273</v>
+        <v>5272</v>
       </c>
       <c r="J451" s="1" t="s">
         <v>2698</v>
@@ -45812,7 +45822,7 @@
         <v>4933</v>
       </c>
       <c r="M451" s="5" t="s">
-        <v>5274</v>
+        <v>5273</v>
       </c>
       <c r="N451" s="1" t="s">
         <v>24</v>
@@ -45848,13 +45858,13 @@
         <v>2704</v>
       </c>
       <c r="K452" s="6" t="s">
-        <v>5284</v>
+        <v>5283</v>
       </c>
       <c r="L452" s="3" t="s">
         <v>4938</v>
       </c>
       <c r="M452" s="5" t="s">
-        <v>5285</v>
+        <v>5284</v>
       </c>
       <c r="N452" s="1" t="s">
         <v>24</v>
@@ -45920,10 +45930,10 @@
         <v>76</v>
       </c>
       <c r="G454" s="5" t="s">
-        <v>5257</v>
+        <v>5256</v>
       </c>
       <c r="H454" s="5" t="s">
-        <v>5237</v>
+        <v>5236</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>2713</v>
@@ -45938,7 +45948,7 @@
         <v>4940</v>
       </c>
       <c r="M454" s="5" t="s">
-        <v>5238</v>
+        <v>5237</v>
       </c>
       <c r="N454" s="1" t="s">
         <v>24</v>
@@ -46601,7 +46611,7 @@
         <v>2815</v>
       </c>
       <c r="J470" s="6" t="s">
-        <v>5258</v>
+        <v>5257</v>
       </c>
       <c r="K470" s="1" t="s">
         <v>2816</v>
@@ -46610,7 +46620,7 @@
         <v>4930</v>
       </c>
       <c r="M470" s="5" t="s">
-        <v>5259</v>
+        <v>5258</v>
       </c>
       <c r="N470" s="1" t="s">
         <v>24</v>
@@ -47372,7 +47382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="489" spans="1:14" ht="55.8">
+    <row r="489" spans="1:14" ht="57.6">
       <c r="A489" s="2" t="s">
         <v>2934</v>
       </c>
@@ -47405,10 +47415,10 @@
         <v>1417</v>
       </c>
       <c r="L489" s="3" t="s">
-        <v>23</v>
+        <v>4938</v>
       </c>
       <c r="M489" s="5" t="s">
-        <v>5236</v>
+        <v>5289</v>
       </c>
       <c r="N489" s="1" t="s">
         <v>24</v>
@@ -47492,7 +47502,7 @@
         <v>4930</v>
       </c>
       <c r="M491" s="5" t="s">
-        <v>5240</v>
+        <v>5239</v>
       </c>
       <c r="N491" s="1" t="s">
         <v>24</v>
@@ -47576,7 +47586,7 @@
         <v>4938</v>
       </c>
       <c r="M493" s="5" t="s">
-        <v>5249</v>
+        <v>5248</v>
       </c>
       <c r="N493" s="1" t="s">
         <v>24</v>
@@ -47690,7 +47700,7 @@
         <v>2970</v>
       </c>
       <c r="I496" s="6" t="s">
-        <v>5275</v>
+        <v>5274</v>
       </c>
       <c r="J496" s="1" t="s">
         <v>2971</v>
@@ -47702,7 +47712,7 @@
         <v>4933</v>
       </c>
       <c r="M496" s="5" t="s">
-        <v>5276</v>
+        <v>5275</v>
       </c>
       <c r="N496" s="1" t="s">
         <v>24</v>
@@ -47906,13 +47916,13 @@
         <v>2539</v>
       </c>
       <c r="K501" s="5" t="s">
-        <v>5250</v>
+        <v>5249</v>
       </c>
       <c r="L501" s="3" t="s">
         <v>4938</v>
       </c>
       <c r="M501" s="5" t="s">
-        <v>5251</v>
+        <v>5250</v>
       </c>
       <c r="N501" s="1" t="s">
         <v>24</v>
@@ -49202,7 +49212,7 @@
         <v>3174</v>
       </c>
       <c r="I532" s="6" t="s">
-        <v>5254</v>
+        <v>5253</v>
       </c>
       <c r="J532" s="1" t="s">
         <v>3172</v>
@@ -49214,7 +49224,7 @@
         <v>4933</v>
       </c>
       <c r="M532" s="5" t="s">
-        <v>5255</v>
+        <v>5254</v>
       </c>
       <c r="N532" s="1" t="s">
         <v>24</v>
@@ -52691,7 +52701,7 @@
         <v>2439</v>
       </c>
       <c r="J615" s="6" t="s">
-        <v>5277</v>
+        <v>5276</v>
       </c>
       <c r="K615" s="1" t="s">
         <v>2441</v>
@@ -52736,7 +52746,7 @@
         <v>2446</v>
       </c>
       <c r="K616" s="6" t="s">
-        <v>5281</v>
+        <v>5280</v>
       </c>
       <c r="L616" s="3" t="s">
         <v>52</v>
@@ -52775,7 +52785,7 @@
         <v>2451</v>
       </c>
       <c r="J617" s="6" t="s">
-        <v>5243</v>
+        <v>5242</v>
       </c>
       <c r="K617" s="1" t="s">
         <v>2453</v>
@@ -52784,7 +52794,7 @@
         <v>4930</v>
       </c>
       <c r="M617" s="5" t="s">
-        <v>5244</v>
+        <v>5243</v>
       </c>
       <c r="N617" s="1" t="s">
         <v>24</v>
@@ -53156,13 +53166,13 @@
         <v>3699</v>
       </c>
       <c r="K626" s="6" t="s">
-        <v>5267</v>
+        <v>5266</v>
       </c>
       <c r="L626" s="3" t="s">
         <v>4938</v>
       </c>
       <c r="M626" s="5" t="s">
-        <v>5268</v>
+        <v>5267</v>
       </c>
       <c r="N626" s="1" t="s">
         <v>24</v>
@@ -53354,7 +53364,7 @@
         <v>253</v>
       </c>
       <c r="G631" s="1" t="s">
-        <v>5269</v>
+        <v>5268</v>
       </c>
       <c r="H631" s="1" t="s">
         <v>3724</v>
@@ -53564,7 +53574,7 @@
         <v>258</v>
       </c>
       <c r="G636" s="5" t="s">
-        <v>5270</v>
+        <v>5269</v>
       </c>
       <c r="H636" s="1" t="s">
         <v>3747</v>
@@ -53858,7 +53868,7 @@
         <v>265</v>
       </c>
       <c r="G643" s="6" t="s">
-        <v>5256</v>
+        <v>5255</v>
       </c>
       <c r="H643" s="1" t="s">
         <v>3781</v>
@@ -54866,7 +54876,7 @@
         <v>289</v>
       </c>
       <c r="G667" s="6" t="s">
-        <v>5262</v>
+        <v>5261</v>
       </c>
       <c r="H667" s="1" t="s">
         <v>3174</v>
@@ -54878,13 +54888,13 @@
         <v>3173</v>
       </c>
       <c r="K667" s="24" t="s">
-        <v>5263</v>
+        <v>5262</v>
       </c>
       <c r="L667" s="3" t="s">
         <v>4938</v>
       </c>
       <c r="M667" s="5" t="s">
-        <v>5264</v>
+        <v>5263</v>
       </c>
       <c r="N667" s="1" t="s">
         <v>24</v>
